--- a/TRACTORSCREDIT SALES - UNPAID.xlsx
+++ b/TRACTORSCREDIT SALES - UNPAID.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://singerlk-my.sharepoint.com/personal/dihank_singersl_com/Documents/Desktop/DIHAN/CREDIT SALES -TRACTORS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="11_21454688365074CF3F2F49F6474AC9BCB426D48E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1ED55418-932C-468D-9551-02D39913AA13}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="11_21454688365074CF3F2F49F6474AC9BCB426D48E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF106F71-AC25-423D-9167-00B9819BC319}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1237,18 +1237,18 @@
     <col min="3" max="3" width="12.36328125" customWidth="1"/>
     <col min="4" max="4" width="20.08984375" customWidth="1"/>
     <col min="5" max="5" width="12.6328125" customWidth="1"/>
-    <col min="6" max="6" width="9" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="12.90625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="45.36328125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="11.36328125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="6.08984375" hidden="1" customWidth="1"/>
-    <col min="11" max="12" width="10.26953125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="8.7265625" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14.54296875" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.81640625" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="20.90625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="21.08984375" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="23.81640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="12.90625" customWidth="1"/>
+    <col min="8" max="8" width="45.36328125" customWidth="1"/>
+    <col min="9" max="9" width="11.36328125" customWidth="1"/>
+    <col min="10" max="10" width="6.08984375" customWidth="1"/>
+    <col min="11" max="12" width="10.26953125" customWidth="1"/>
+    <col min="13" max="13" width="8.7265625" customWidth="1"/>
+    <col min="14" max="14" width="14.54296875" customWidth="1"/>
+    <col min="15" max="15" width="14.81640625" customWidth="1"/>
+    <col min="16" max="16" width="20.90625" customWidth="1"/>
+    <col min="17" max="17" width="21.08984375" customWidth="1"/>
+    <col min="18" max="18" width="23.81640625" customWidth="1"/>
     <col min="19" max="19" width="13.90625" customWidth="1"/>
   </cols>
   <sheetData>
